--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-20T17:48:12+00:00</t>
+    <t>2023-01-25T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T18:46:21+00:00</t>
+    <t>2023-02-07T12:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-Contactado.xlsx
+++ b/refs/heads/main/StructureDefinition-Contactado.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
